--- a/MainTop/29.04.2026 Таня ВБ/p6.xlsx
+++ b/MainTop/29.04.2026 Таня ВБ/p6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,14 +513,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Термонаклейка Сердце Бабочки летят</t>
+          <t>Термонаклейка Шредер и Кренг из Черепашек-ниндзя</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -542,20 +542,20 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>-28.9</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Термонаклейка Рука Фатимы</t>
+          <t>Термонаклейка Сердце Бабочки летят</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -577,20 +577,20 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>-29.8</v>
+        <v>-28.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Термонаклейка Карточная королева кричит</t>
+          <t>Термонаклейка Рука Фатимы</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -612,17 +612,17 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>-23.4</v>
+        <v>-29.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Термонаклейка Цветы Розовые Spring Blossoms</t>
+          <t>Термонаклейка Карточная королева кричит</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="C6" t="n">
         <v>14</v>
@@ -647,20 +647,20 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>-23.2</v>
+        <v>-23.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Термонаклейка Девушка силует обнимают природа</t>
+          <t>Термонаклейка Цветы Розовые Spring Blossoms</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -682,20 +682,20 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>-16.8</v>
+        <v>-23.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Термонаклейка Сова в цветах</t>
+          <t>Термонаклейка Девушка силует обнимают природа</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -717,20 +717,20 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>-14.7</v>
+        <v>-16.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Термонаклейка Рука жест рок металл</t>
+          <t>Термонаклейка Сова в цветах</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -752,20 +752,20 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>-15.9</v>
+        <v>-14.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Термонаклейка Кит в голубых и розовых оттенках</t>
+          <t>Термонаклейка Рука жест рок металл</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.9</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -787,20 +787,20 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>-18.9</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Термонаклейка Микки Маус бабочки цверы силует</t>
+          <t>Термонаклейка Кит в голубых и розовых оттенках</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>-14.8</v>
+        <v>-18.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Термонаклейка Змеи черная белая 2шт</t>
+          <t>Термонаклейка Микки Маус бабочки цверы силует</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -863,14 +863,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Термонаклейка Графичное лицо в чёрно-белом</t>
+          <t>Термонаклейка Змеи черная белая 2шт</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -892,20 +892,20 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>-13.5</v>
+        <v>-14.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Термонаклейка Леопард пятна сердечки полностью</t>
+          <t>Термонаклейка Графичное лицо в чёрно-белом</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -927,20 +927,20 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>-11.3</v>
+        <v>-13.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Термонаклейка Одри Хепбёрн холст Vogue</t>
+          <t>Термонаклейка Леопард пятна сердечки полностью</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -962,20 +962,20 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>-17.9</v>
+        <v>-11.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Термонаклейка Чёрный кот Catzilla Годзилла луч</t>
+          <t>Термонаклейка Одри Хепбёрн холст Vogue</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -997,20 +997,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>-14.8</v>
+        <v>-17.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Термонаклейка Девушка в поле розовых цветов</t>
+          <t>Термонаклейка Чёрный кот Catzilla Годзилла луч</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1032,20 +1032,20 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>-13.6</v>
+        <v>-14.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Термонаклейка Мэрилин Монро Медуза Горгона</t>
+          <t>Термонаклейка Девушка в поле розовых цветов</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1067,20 +1067,20 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>-12.4</v>
+        <v>-13.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Термонаклейка Ветви с белыми цветами</t>
+          <t>Термонаклейка Мэрилин Монро Медуза Горгона</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1102,20 +1102,20 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>-10.1</v>
+        <v>-12.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Термонаклейка Фламинго трое на воде право</t>
+          <t>Термонаклейка Ветви с белыми цветами</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1137,20 +1137,20 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>-9</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Термонаклейка Летающий кит и город</t>
+          <t>Термонаклейка Фламинго трое на воде право</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1172,17 +1172,17 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Термонаклейка Мопс Собачка попа секси</t>
+          <t>Термонаклейка Акира Глаз ядерный взрыв</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -1207,20 +1207,20 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>-9.1</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Термонаклейка Адам и Ева яблоко змея</t>
+          <t>Термонаклейка Летающий кит и город</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1242,20 +1242,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>-10.1</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Термонаклейка Девушка в маках сон</t>
+          <t>Термонаклейка Мопс Собачка попа секси</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1277,13 +1277,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>-12</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Термонаклейка Астронавт и часы</t>
+          <t>Термонаклейка Адам и Ева яблоко змея</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1318,14 +1318,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Термонаклейка Девушка яркий арт стиль</t>
+          <t>Термонаклейка Девушка в маках сон</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1347,20 +1347,20 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Термонаклейка Акира и мотоцикл Аниме</t>
+          <t>Термонаклейка Астронавт и часы</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0.1</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1382,17 +1382,17 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>-8.1</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Термонаклейка Сердце в руках арт</t>
+          <t>Термонаклейка Девушка яркий арт стиль</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
@@ -1417,20 +1417,20 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>-11.1</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Термонаклейка Заяц неон арт персонаж</t>
+          <t>Термонаклейка Акира и мотоцикл Аниме</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0.1</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1452,20 +1452,20 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>-10.1</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Термонаклейка Человек Паук Лого позади</t>
+          <t>Термонаклейка Акира на троне среди металлолома</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1474,11 +1474,11 @@
         <v>12</v>
       </c>
       <c r="F30" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2_а5</t>
+          <t>1_а4</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1487,20 +1487,20 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>32.3</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Термонаклейка Зайка балерина</t>
+          <t>Термонаклейка Сердце в руках арт</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4.6</v>
+        <v>0.1</v>
       </c>
       <c r="C31" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1509,11 +1509,11 @@
         <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2_а5</t>
+          <t>1_а4</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1522,20 +1522,20 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>-11.6</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Термонаклейка Зайчик ромашка в руках</t>
+          <t>Термонаклейка Заяц неон арт персонаж</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.9</v>
+        <v>0.1</v>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -1544,11 +1544,11 @@
         <v>12</v>
       </c>
       <c r="F32" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2_а5</t>
+          <t>1_а4</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1557,20 +1557,20 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>12.1</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Термонаклейка Лило и Стич сидят</t>
+          <t>Термонаклейка Шрек мем поднимает голову</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1579,11 +1579,11 @@
         <v>12</v>
       </c>
       <c r="F33" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2_а5</t>
+          <t>1_а4</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1592,20 +1592,20 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>-2.899999999999999</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Термонаклейка Дисней утка Дейзи и Минни пис</t>
+          <t>Термонаклейка Кибер-девушка в стиле аниме</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1614,11 +1614,11 @@
         <v>12</v>
       </c>
       <c r="F34" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2_а5</t>
+          <t>1_а4</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1627,20 +1627,20 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>10</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Термонаклейка Весёлый енот выглядывает</t>
+          <t>Термонаклейка Череп с рогами и логотипом Metallica</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1649,11 +1649,11 @@
         <v>12</v>
       </c>
       <c r="F35" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2_а5</t>
+          <t>1_а4</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1662,20 +1662,20 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>-24.8</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Термонаклейка Разноцветные сердечки</t>
+          <t>Термонаклейка Берсерк воин в аниме стиле</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1684,11 +1684,11 @@
         <v>12</v>
       </c>
       <c r="F36" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2_а5</t>
+          <t>1_а4</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1697,20 +1697,20 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>-17.8</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Термонаклейка Миньон с бананами</t>
+          <t>Термонаклейка Акира мотоцикл и разрушения</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1719,11 +1719,11 @@
         <v>12</v>
       </c>
       <c r="F37" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2_а5</t>
+          <t>1_а4</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1732,20 +1732,20 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.199999999999999</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Термонаклейка Котята на качелях</t>
+          <t>Термонаклейка Киберпанк череп с ирокезом</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -1754,20 +1754,300 @@
         <v>12</v>
       </c>
       <c r="F38" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>1_а4</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Термонаклейка Кибердевушка с капюшоном</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>12</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1_а4</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Термонаклейка Яркие коты неон арт</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>12</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1_а4</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Термонаклейка Человек Паук Лого позади</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>12</v>
+      </c>
+      <c r="F41" t="n">
+        <v>48</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>2_а5</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>29.04.2026 Таня ВБ</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>-17.1</v>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>32.3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Термонаклейка Зайка балерина</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="C42" t="n">
+        <v>27</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>12</v>
+      </c>
+      <c r="F42" t="n">
+        <v>32</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>-11.6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Термонаклейка Зайчик ромашка в руках</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>12</v>
+      </c>
+      <c r="F43" t="n">
+        <v>32</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Термонаклейка Лило и Стич сидят</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>12</v>
+      </c>
+      <c r="F44" t="n">
+        <v>24</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>-2.899999999999999</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Термонаклейка Дисней утка Дейзи и Минни пис</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>12</v>
+      </c>
+      <c r="F45" t="n">
+        <v>24</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Термонаклейка Весёлый енот выглядывает</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C46" t="n">
+        <v>29</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>12</v>
+      </c>
+      <c r="F46" t="n">
+        <v>20</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2_а5</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>29.04.2026 Таня ВБ</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>-24.8</v>
       </c>
     </row>
   </sheetData>
